--- a/Plotting/Results_excels/production_shares_ammonia_LowAmbition_FPO.xlsx
+++ b/Plotting/Results_excels/production_shares_ammonia_LowAmbition_FPO.xlsx
@@ -539,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Conventional</t>
+          <t>Conventional (fossil)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -552,7 +552,7 @@
         <v>-2.620601923793058e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1183999.999999965</v>
+        <v>1184000.000000123</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1184000.000000069</v>
+        <v>1183999.99999983</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
+          <t>Conventional (fossil) with CC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -620,22 +620,22 @@
         <v>71.29135345365613</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3.125974278518378e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1181739.812830687</v>
+        <v>1181730.993395598</v>
       </c>
       <c r="G6" t="n">
-        <v>1181730.993934789</v>
+        <v>1181730.993934939</v>
       </c>
       <c r="H6" t="n">
-        <v>2.410724184753102e-08</v>
+        <v>3.990587333568184e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1181739.519423959</v>
+        <v>1181738.037682114</v>
       </c>
       <c r="J6" t="n">
-        <v>1181730.99393559</v>
+        <v>1181730.993935554</v>
       </c>
     </row>
     <row r="7">
@@ -654,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-2.522503943562989e-09</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.97772225420112e-09</v>
+        <v>7.297289221170428e-08</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
